--- a/Lab_4/data/partB/optimized_param_results/v200_k20_s150_results.xlsx
+++ b/Lab_4/data/partB/optimized_param_results/v200_k20_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9</v>
-      </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,16 +677,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -698,25 +698,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -750,22 +750,22 @@
         <v>6</v>
       </c>
       <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -778,49 +778,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>58</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>9</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,37 +842,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
       <c r="I9" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,25 +958,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -995,25 +995,25 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1041,46 +1041,46 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
         <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1105,19 +1105,19 @@
         <v>9</v>
       </c>
       <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>7</v>
       </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1126,13 +1126,13 @@
         <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1145,19 +1145,19 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1218,22 +1218,22 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -1255,40 +1255,40 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17791,7 +17791,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18097,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22585,7 +22585,7 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="C1352" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
